--- a/Used_cars_data.xlsx
+++ b/Used_cars_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\Used_Car_Generation_Citywise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB4137C-ADB6-475A-965C-00201C11088D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20DD2E2A-B3C0-41EA-8418-EEC28F2C1372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{5C907EC6-8375-449B-912A-5B85C1E38DC1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{5C907EC6-8375-449B-912A-5B85C1E38DC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Reference" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="32">
   <si>
     <t>Day</t>
   </si>
@@ -684,10 +684,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F03664B9-21D8-4CE9-9CC2-213E093E66E2}">
-  <dimension ref="A1:D315"/>
+  <dimension ref="A1:D319"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -5100,14 +5101,71 @@
         <v>18</v>
       </c>
     </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A316" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B316" t="s">
+        <v>11</v>
+      </c>
+      <c r="C316">
+        <v>2275.46</v>
+      </c>
+      <c r="D316">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A317" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B317" t="s">
+        <v>7</v>
+      </c>
+      <c r="C317">
+        <v>892.94</v>
+      </c>
+      <c r="D317">
+        <v>12.34</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A318" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B318" t="s">
+        <v>8</v>
+      </c>
+      <c r="C318">
+        <v>1609.95</v>
+      </c>
+      <c r="D318">
+        <v>65.25</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A319" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B319" t="s">
+        <v>9</v>
+      </c>
+      <c r="C319">
+        <v>1236.8499999999999</v>
+      </c>
+      <c r="D319">
+        <v>27.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19733ED7-6DA4-4FF9-B8AE-1C6E36A489FB}">
-  <dimension ref="A1:D261"/>
+  <dimension ref="A1:D268"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -8758,6 +8816,104 @@
         <v>50</v>
       </c>
     </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A262" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B262" t="s">
+        <v>20</v>
+      </c>
+      <c r="C262" s="2">
+        <v>2085.2199999999998</v>
+      </c>
+      <c r="D262">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A263" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B263" t="s">
+        <v>21</v>
+      </c>
+      <c r="C263" s="2">
+        <v>2022.7</v>
+      </c>
+      <c r="D263">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A264" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B264" t="s">
+        <v>16</v>
+      </c>
+      <c r="C264" s="2">
+        <v>2096.13</v>
+      </c>
+      <c r="D264">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A265" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B265" t="s">
+        <v>17</v>
+      </c>
+      <c r="C265" s="2">
+        <v>2472.44</v>
+      </c>
+      <c r="D265">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A266" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B266" t="s">
+        <v>18</v>
+      </c>
+      <c r="C266" s="2">
+        <v>1002.93</v>
+      </c>
+      <c r="D266">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A267" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B267" t="s">
+        <v>28</v>
+      </c>
+      <c r="C267">
+        <v>987.9</v>
+      </c>
+      <c r="D267">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A268" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B268" t="s">
+        <v>29</v>
+      </c>
+      <c r="C268">
+        <v>350.28</v>
+      </c>
+      <c r="D268">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Used_cars_data.xlsx
+++ b/Used_cars_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\Used_Car_Generation_Citywise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20DD2E2A-B3C0-41EA-8418-EEC28F2C1372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA65EBB-2BD9-403D-BB2D-C24EB36D62D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{5C907EC6-8375-449B-912A-5B85C1E38DC1}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="32">
   <si>
     <t>Day</t>
   </si>
@@ -5165,8 +5165,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19733ED7-6DA4-4FF9-B8AE-1C6E36A489FB}">
-  <dimension ref="A1:D268"/>
+  <dimension ref="A1:D265"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="28.7265625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -8706,16 +8709,16 @@
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B254" t="s">
-        <v>29</v>
-      </c>
-      <c r="C254">
-        <v>168.85</v>
+        <v>20</v>
+      </c>
+      <c r="C254" s="2">
+        <v>2009.9</v>
       </c>
       <c r="D254">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.35">
@@ -8723,13 +8726,13 @@
         <v>46211</v>
       </c>
       <c r="B255" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C255" s="2">
-        <v>2009.9</v>
+        <v>1970.39</v>
       </c>
       <c r="D255">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.35">
@@ -8737,13 +8740,13 @@
         <v>46211</v>
       </c>
       <c r="B256" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C256" s="2">
-        <v>1970.39</v>
+        <v>1909.19</v>
       </c>
       <c r="D256">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.35">
@@ -8751,13 +8754,13 @@
         <v>46211</v>
       </c>
       <c r="B257" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C257" s="2">
-        <v>1909.19</v>
+        <v>2664.03</v>
       </c>
       <c r="D257">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.35">
@@ -8765,13 +8768,13 @@
         <v>46211</v>
       </c>
       <c r="B258" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C258" s="2">
-        <v>2664.03</v>
+        <v>1023.64</v>
       </c>
       <c r="D258">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.35">
@@ -8779,41 +8782,41 @@
         <v>46211</v>
       </c>
       <c r="B259" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C259" s="2">
-        <v>1023.64</v>
+        <v>1055.05</v>
       </c>
       <c r="D259">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A260" s="1">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B260" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C260" s="2">
-        <v>1055.05</v>
+        <v>2085.2199999999998</v>
       </c>
       <c r="D260">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A261" s="1">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B261" t="s">
-        <v>29</v>
-      </c>
-      <c r="C261">
-        <v>778.72</v>
+        <v>21</v>
+      </c>
+      <c r="C261" s="2">
+        <v>2022.7</v>
       </c>
       <c r="D261">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.35">
@@ -8821,13 +8824,13 @@
         <v>46212</v>
       </c>
       <c r="B262" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C262" s="2">
-        <v>2085.2199999999998</v>
+        <v>2096.13</v>
       </c>
       <c r="D262">
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.35">
@@ -8835,13 +8838,13 @@
         <v>46212</v>
       </c>
       <c r="B263" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C263" s="2">
-        <v>2022.7</v>
+        <v>2472.44</v>
       </c>
       <c r="D263">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.35">
@@ -8849,13 +8852,13 @@
         <v>46212</v>
       </c>
       <c r="B264" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C264" s="2">
-        <v>2096.13</v>
+        <v>1002.93</v>
       </c>
       <c r="D264">
-        <v>43</v>
+        <v>18</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.35">
@@ -8863,55 +8866,13 @@
         <v>46212</v>
       </c>
       <c r="B265" t="s">
-        <v>17</v>
-      </c>
-      <c r="C265" s="2">
-        <v>2472.44</v>
+        <v>28</v>
+      </c>
+      <c r="C265">
+        <v>987.9</v>
       </c>
       <c r="D265">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A266" s="1">
-        <v>46212</v>
-      </c>
-      <c r="B266" t="s">
-        <v>18</v>
-      </c>
-      <c r="C266" s="2">
-        <v>1002.93</v>
-      </c>
-      <c r="D266">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A267" s="1">
-        <v>46212</v>
-      </c>
-      <c r="B267" t="s">
-        <v>28</v>
-      </c>
-      <c r="C267">
-        <v>987.9</v>
-      </c>
-      <c r="D267">
         <v>1</v>
-      </c>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A268" s="1">
-        <v>46212</v>
-      </c>
-      <c r="B268" t="s">
-        <v>29</v>
-      </c>
-      <c r="C268">
-        <v>350.28</v>
-      </c>
-      <c r="D268">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Used_cars_data.xlsx
+++ b/Used_cars_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\Used_Car_Generation_Citywise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA65EBB-2BD9-403D-BB2D-C24EB36D62D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54792844-BA34-4D14-8729-916CF2C7432E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{5C907EC6-8375-449B-912A-5B85C1E38DC1}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="32">
   <si>
     <t>Day</t>
   </si>
@@ -684,7 +684,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F03664B9-21D8-4CE9-9CC2-213E093E66E2}">
-  <dimension ref="A1:D319"/>
+  <dimension ref="A1:D331"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -5157,6 +5157,174 @@
         <v>27.93</v>
       </c>
     </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A320" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B320" t="s">
+        <v>11</v>
+      </c>
+      <c r="C320">
+        <v>2043.42</v>
+      </c>
+      <c r="D320">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A321" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B321" t="s">
+        <v>11</v>
+      </c>
+      <c r="C321">
+        <v>1036.27</v>
+      </c>
+      <c r="D321">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A322" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B322" t="s">
+        <v>11</v>
+      </c>
+      <c r="C322">
+        <v>1263.17</v>
+      </c>
+      <c r="D322">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A323" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B323" t="s">
+        <v>7</v>
+      </c>
+      <c r="C323">
+        <v>1117.5899999999999</v>
+      </c>
+      <c r="D323">
+        <v>12.45</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A324" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B324" t="s">
+        <v>7</v>
+      </c>
+      <c r="C324">
+        <v>1622.65</v>
+      </c>
+      <c r="D324">
+        <v>14.56</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A325" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B325" t="s">
+        <v>7</v>
+      </c>
+      <c r="C325">
+        <v>1215.1400000000001</v>
+      </c>
+      <c r="D325">
+        <v>31.19</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A326" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B326" t="s">
+        <v>8</v>
+      </c>
+      <c r="C326">
+        <v>1570.47</v>
+      </c>
+      <c r="D326">
+        <v>36.57</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A327" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B327" t="s">
+        <v>8</v>
+      </c>
+      <c r="C327">
+        <v>1592.62</v>
+      </c>
+      <c r="D327">
+        <v>46.81</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A328" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B328" t="s">
+        <v>8</v>
+      </c>
+      <c r="C328">
+        <v>1607.36</v>
+      </c>
+      <c r="D328">
+        <v>51.86</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A329" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B329" t="s">
+        <v>9</v>
+      </c>
+      <c r="C329">
+        <v>1273</v>
+      </c>
+      <c r="D329">
+        <v>23.93</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A330" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B330" t="s">
+        <v>9</v>
+      </c>
+      <c r="C330">
+        <v>1276.31</v>
+      </c>
+      <c r="D330">
+        <v>26.64</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A331" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B331" t="s">
+        <v>9</v>
+      </c>
+      <c r="C331">
+        <v>1257.6400000000001</v>
+      </c>
+      <c r="D331">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5165,7 +5333,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19733ED7-6DA4-4FF9-B8AE-1C6E36A489FB}">
-  <dimension ref="A1:D265"/>
+  <dimension ref="A1:D283"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="28.7265625" bestFit="1" customWidth="1"/>
@@ -8875,6 +9043,258 @@
         <v>1</v>
       </c>
     </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A266" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B266" t="s">
+        <v>29</v>
+      </c>
+      <c r="C266">
+        <v>654.12</v>
+      </c>
+      <c r="D266">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A267" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B267" t="s">
+        <v>18</v>
+      </c>
+      <c r="C267">
+        <v>1082.83</v>
+      </c>
+      <c r="D267">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A268" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B268" t="s">
+        <v>17</v>
+      </c>
+      <c r="C268">
+        <v>2160.94</v>
+      </c>
+      <c r="D268">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A269" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B269" t="s">
+        <v>16</v>
+      </c>
+      <c r="C269">
+        <v>2077.88</v>
+      </c>
+      <c r="D269">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A270" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B270" t="s">
+        <v>21</v>
+      </c>
+      <c r="C270">
+        <v>2051.4899999999998</v>
+      </c>
+      <c r="D270">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A271" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B271" t="s">
+        <v>20</v>
+      </c>
+      <c r="C271">
+        <v>2140.66</v>
+      </c>
+      <c r="D271">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A272" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B272" t="s">
+        <v>29</v>
+      </c>
+      <c r="C272">
+        <v>911.2</v>
+      </c>
+      <c r="D272">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A273" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B273" t="s">
+        <v>18</v>
+      </c>
+      <c r="C273">
+        <v>857.82</v>
+      </c>
+      <c r="D273">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A274" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B274" t="s">
+        <v>17</v>
+      </c>
+      <c r="C274">
+        <v>1634.03</v>
+      </c>
+      <c r="D274">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A275" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B275" t="s">
+        <v>16</v>
+      </c>
+      <c r="C275">
+        <v>1856.6</v>
+      </c>
+      <c r="D275">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A276" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B276" t="s">
+        <v>21</v>
+      </c>
+      <c r="C276">
+        <v>2130.1</v>
+      </c>
+      <c r="D276">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A277" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B277" t="s">
+        <v>20</v>
+      </c>
+      <c r="C277">
+        <v>1720.53</v>
+      </c>
+      <c r="D277">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A278" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B278" t="s">
+        <v>29</v>
+      </c>
+      <c r="C278">
+        <v>450.31</v>
+      </c>
+      <c r="D278">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A279" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B279" t="s">
+        <v>18</v>
+      </c>
+      <c r="C279">
+        <v>932.92</v>
+      </c>
+      <c r="D279">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A280" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B280" t="s">
+        <v>17</v>
+      </c>
+      <c r="C280">
+        <v>1930.36</v>
+      </c>
+      <c r="D280">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A281" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B281" t="s">
+        <v>16</v>
+      </c>
+      <c r="C281">
+        <v>1930.19</v>
+      </c>
+      <c r="D281">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A282" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B282" t="s">
+        <v>21</v>
+      </c>
+      <c r="C282">
+        <v>1950.89</v>
+      </c>
+      <c r="D282">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A283" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B283" t="s">
+        <v>20</v>
+      </c>
+      <c r="C283">
+        <v>1905.24</v>
+      </c>
+      <c r="D283">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Used_cars_data.xlsx
+++ b/Used_cars_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\Used_Car_Generation_Citywise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54792844-BA34-4D14-8729-916CF2C7432E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E766B63-0371-4268-822C-7E5EAF9C76AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{5C907EC6-8375-449B-912A-5B85C1E38DC1}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="32">
   <si>
     <t>Day</t>
   </si>
@@ -5333,7 +5333,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19733ED7-6DA4-4FF9-B8AE-1C6E36A489FB}">
-  <dimension ref="A1:D283"/>
+  <dimension ref="A1:D280"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="28.7265625" bestFit="1" customWidth="1"/>
@@ -9048,13 +9048,13 @@
         <v>46215</v>
       </c>
       <c r="B266" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C266">
-        <v>654.12</v>
+        <v>1082.83</v>
       </c>
       <c r="D266">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.35">
@@ -9062,13 +9062,13 @@
         <v>46215</v>
       </c>
       <c r="B267" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C267">
-        <v>1082.83</v>
+        <v>2160.94</v>
       </c>
       <c r="D267">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.35">
@@ -9076,13 +9076,13 @@
         <v>46215</v>
       </c>
       <c r="B268" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C268">
-        <v>2160.94</v>
+        <v>2077.88</v>
       </c>
       <c r="D268">
-        <v>35</v>
+        <v>49</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.35">
@@ -9090,13 +9090,13 @@
         <v>46215</v>
       </c>
       <c r="B269" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C269">
-        <v>2077.88</v>
+        <v>2051.4899999999998</v>
       </c>
       <c r="D269">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.35">
@@ -9104,27 +9104,27 @@
         <v>46215</v>
       </c>
       <c r="B270" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C270">
-        <v>2051.4899999999998</v>
+        <v>2140.66</v>
       </c>
       <c r="D270">
-        <v>54</v>
+        <v>20</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A271" s="1">
-        <v>46215</v>
+        <v>46214</v>
       </c>
       <c r="B271" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C271">
-        <v>2140.66</v>
+        <v>857.82</v>
       </c>
       <c r="D271">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.35">
@@ -9132,13 +9132,13 @@
         <v>46214</v>
       </c>
       <c r="B272" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C272">
-        <v>911.2</v>
+        <v>1634.03</v>
       </c>
       <c r="D272">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.35">
@@ -9146,13 +9146,13 @@
         <v>46214</v>
       </c>
       <c r="B273" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C273">
-        <v>857.82</v>
+        <v>1856.6</v>
       </c>
       <c r="D273">
-        <v>18</v>
+        <v>45</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.35">
@@ -9160,13 +9160,13 @@
         <v>46214</v>
       </c>
       <c r="B274" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C274">
-        <v>1634.03</v>
+        <v>2130.1</v>
       </c>
       <c r="D274">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.35">
@@ -9174,41 +9174,41 @@
         <v>46214</v>
       </c>
       <c r="B275" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C275">
-        <v>1856.6</v>
+        <v>1720.53</v>
       </c>
       <c r="D275">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A276" s="1">
-        <v>46214</v>
+        <v>46213</v>
       </c>
       <c r="B276" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C276">
-        <v>2130.1</v>
+        <v>932.92</v>
       </c>
       <c r="D276">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A277" s="1">
-        <v>46214</v>
+        <v>46213</v>
       </c>
       <c r="B277" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C277">
-        <v>1720.53</v>
+        <v>1930.36</v>
       </c>
       <c r="D277">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.35">
@@ -9216,13 +9216,13 @@
         <v>46213</v>
       </c>
       <c r="B278" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C278">
-        <v>450.31</v>
+        <v>1930.19</v>
       </c>
       <c r="D278">
-        <v>11</v>
+        <v>54</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.35">
@@ -9230,13 +9230,13 @@
         <v>46213</v>
       </c>
       <c r="B279" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C279">
-        <v>932.92</v>
+        <v>1950.89</v>
       </c>
       <c r="D279">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.35">
@@ -9244,54 +9244,12 @@
         <v>46213</v>
       </c>
       <c r="B280" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C280">
-        <v>1930.36</v>
+        <v>1905.24</v>
       </c>
       <c r="D280">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A281" s="1">
-        <v>46213</v>
-      </c>
-      <c r="B281" t="s">
-        <v>16</v>
-      </c>
-      <c r="C281">
-        <v>1930.19</v>
-      </c>
-      <c r="D281">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A282" s="1">
-        <v>46213</v>
-      </c>
-      <c r="B282" t="s">
-        <v>21</v>
-      </c>
-      <c r="C282">
-        <v>1950.89</v>
-      </c>
-      <c r="D282">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A283" s="1">
-        <v>46213</v>
-      </c>
-      <c r="B283" t="s">
-        <v>20</v>
-      </c>
-      <c r="C283">
-        <v>1905.24</v>
-      </c>
-      <c r="D283">
         <v>23</v>
       </c>
     </row>

--- a/Used_cars_data.xlsx
+++ b/Used_cars_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\Used_Car_Generation_Citywise\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E766B63-0371-4268-822C-7E5EAF9C76AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB4137C-ADB6-475A-965C-00201C11088D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{5C907EC6-8375-449B-912A-5B85C1E38DC1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{5C907EC6-8375-449B-912A-5B85C1E38DC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Reference" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="32">
   <si>
     <t>Day</t>
   </si>
@@ -684,11 +684,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F03664B9-21D8-4CE9-9CC2-213E093E66E2}">
-  <dimension ref="A1:D331"/>
+  <dimension ref="A1:D315"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -5101,243 +5100,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A316" s="1">
-        <v>46212</v>
-      </c>
-      <c r="B316" t="s">
-        <v>11</v>
-      </c>
-      <c r="C316">
-        <v>2275.46</v>
-      </c>
-      <c r="D316">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A317" s="1">
-        <v>46212</v>
-      </c>
-      <c r="B317" t="s">
-        <v>7</v>
-      </c>
-      <c r="C317">
-        <v>892.94</v>
-      </c>
-      <c r="D317">
-        <v>12.34</v>
-      </c>
-    </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A318" s="1">
-        <v>46212</v>
-      </c>
-      <c r="B318" t="s">
-        <v>8</v>
-      </c>
-      <c r="C318">
-        <v>1609.95</v>
-      </c>
-      <c r="D318">
-        <v>65.25</v>
-      </c>
-    </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A319" s="1">
-        <v>46212</v>
-      </c>
-      <c r="B319" t="s">
-        <v>9</v>
-      </c>
-      <c r="C319">
-        <v>1236.8499999999999</v>
-      </c>
-      <c r="D319">
-        <v>27.93</v>
-      </c>
-    </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A320" s="1">
-        <v>46213</v>
-      </c>
-      <c r="B320" t="s">
-        <v>11</v>
-      </c>
-      <c r="C320">
-        <v>2043.42</v>
-      </c>
-      <c r="D320">
-        <v>7.2</v>
-      </c>
-    </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A321" s="1">
-        <v>46214</v>
-      </c>
-      <c r="B321" t="s">
-        <v>11</v>
-      </c>
-      <c r="C321">
-        <v>1036.27</v>
-      </c>
-      <c r="D321">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A322" s="1">
-        <v>46215</v>
-      </c>
-      <c r="B322" t="s">
-        <v>11</v>
-      </c>
-      <c r="C322">
-        <v>1263.17</v>
-      </c>
-      <c r="D322">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A323" s="1">
-        <v>46213</v>
-      </c>
-      <c r="B323" t="s">
-        <v>7</v>
-      </c>
-      <c r="C323">
-        <v>1117.5899999999999</v>
-      </c>
-      <c r="D323">
-        <v>12.45</v>
-      </c>
-    </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A324" s="1">
-        <v>46214</v>
-      </c>
-      <c r="B324" t="s">
-        <v>7</v>
-      </c>
-      <c r="C324">
-        <v>1622.65</v>
-      </c>
-      <c r="D324">
-        <v>14.56</v>
-      </c>
-    </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A325" s="1">
-        <v>46215</v>
-      </c>
-      <c r="B325" t="s">
-        <v>7</v>
-      </c>
-      <c r="C325">
-        <v>1215.1400000000001</v>
-      </c>
-      <c r="D325">
-        <v>31.19</v>
-      </c>
-    </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A326" s="1">
-        <v>46213</v>
-      </c>
-      <c r="B326" t="s">
-        <v>8</v>
-      </c>
-      <c r="C326">
-        <v>1570.47</v>
-      </c>
-      <c r="D326">
-        <v>36.57</v>
-      </c>
-    </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A327" s="1">
-        <v>46214</v>
-      </c>
-      <c r="B327" t="s">
-        <v>8</v>
-      </c>
-      <c r="C327">
-        <v>1592.62</v>
-      </c>
-      <c r="D327">
-        <v>46.81</v>
-      </c>
-    </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A328" s="1">
-        <v>46215</v>
-      </c>
-      <c r="B328" t="s">
-        <v>8</v>
-      </c>
-      <c r="C328">
-        <v>1607.36</v>
-      </c>
-      <c r="D328">
-        <v>51.86</v>
-      </c>
-    </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A329" s="1">
-        <v>46213</v>
-      </c>
-      <c r="B329" t="s">
-        <v>9</v>
-      </c>
-      <c r="C329">
-        <v>1273</v>
-      </c>
-      <c r="D329">
-        <v>23.93</v>
-      </c>
-    </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A330" s="1">
-        <v>46214</v>
-      </c>
-      <c r="B330" t="s">
-        <v>9</v>
-      </c>
-      <c r="C330">
-        <v>1276.31</v>
-      </c>
-      <c r="D330">
-        <v>26.64</v>
-      </c>
-    </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A331" s="1">
-        <v>46215</v>
-      </c>
-      <c r="B331" t="s">
-        <v>9</v>
-      </c>
-      <c r="C331">
-        <v>1257.6400000000001</v>
-      </c>
-      <c r="D331">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19733ED7-6DA4-4FF9-B8AE-1C6E36A489FB}">
-  <dimension ref="A1:D280"/>
+  <dimension ref="A1:D261"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="28.7265625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -8877,16 +8648,16 @@
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="B254" t="s">
-        <v>20</v>
-      </c>
-      <c r="C254" s="2">
-        <v>2009.9</v>
+        <v>29</v>
+      </c>
+      <c r="C254">
+        <v>168.85</v>
       </c>
       <c r="D254">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.35">
@@ -8894,13 +8665,13 @@
         <v>46211</v>
       </c>
       <c r="B255" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C255" s="2">
-        <v>1970.39</v>
+        <v>2009.9</v>
       </c>
       <c r="D255">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.35">
@@ -8908,13 +8679,13 @@
         <v>46211</v>
       </c>
       <c r="B256" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C256" s="2">
-        <v>1909.19</v>
+        <v>1970.39</v>
       </c>
       <c r="D256">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.35">
@@ -8922,13 +8693,13 @@
         <v>46211</v>
       </c>
       <c r="B257" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C257" s="2">
-        <v>2664.03</v>
+        <v>1909.19</v>
       </c>
       <c r="D257">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.35">
@@ -8936,13 +8707,13 @@
         <v>46211</v>
       </c>
       <c r="B258" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C258" s="2">
-        <v>1023.64</v>
+        <v>2664.03</v>
       </c>
       <c r="D258">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.35">
@@ -8950,307 +8721,41 @@
         <v>46211</v>
       </c>
       <c r="B259" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C259" s="2">
-        <v>1055.05</v>
+        <v>1023.64</v>
       </c>
       <c r="D259">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A260" s="1">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B260" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C260" s="2">
-        <v>2085.2199999999998</v>
+        <v>1055.05</v>
       </c>
       <c r="D260">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A261" s="1">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B261" t="s">
-        <v>21</v>
-      </c>
-      <c r="C261" s="2">
-        <v>2022.7</v>
+        <v>29</v>
+      </c>
+      <c r="C261">
+        <v>778.72</v>
       </c>
       <c r="D261">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A262" s="1">
-        <v>46212</v>
-      </c>
-      <c r="B262" t="s">
-        <v>16</v>
-      </c>
-      <c r="C262" s="2">
-        <v>2096.13</v>
-      </c>
-      <c r="D262">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A263" s="1">
-        <v>46212</v>
-      </c>
-      <c r="B263" t="s">
-        <v>17</v>
-      </c>
-      <c r="C263" s="2">
-        <v>2472.44</v>
-      </c>
-      <c r="D263">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A264" s="1">
-        <v>46212</v>
-      </c>
-      <c r="B264" t="s">
-        <v>18</v>
-      </c>
-      <c r="C264" s="2">
-        <v>1002.93</v>
-      </c>
-      <c r="D264">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A265" s="1">
-        <v>46212</v>
-      </c>
-      <c r="B265" t="s">
-        <v>28</v>
-      </c>
-      <c r="C265">
-        <v>987.9</v>
-      </c>
-      <c r="D265">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A266" s="1">
-        <v>46215</v>
-      </c>
-      <c r="B266" t="s">
-        <v>18</v>
-      </c>
-      <c r="C266">
-        <v>1082.83</v>
-      </c>
-      <c r="D266">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A267" s="1">
-        <v>46215</v>
-      </c>
-      <c r="B267" t="s">
-        <v>17</v>
-      </c>
-      <c r="C267">
-        <v>2160.94</v>
-      </c>
-      <c r="D267">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A268" s="1">
-        <v>46215</v>
-      </c>
-      <c r="B268" t="s">
-        <v>16</v>
-      </c>
-      <c r="C268">
-        <v>2077.88</v>
-      </c>
-      <c r="D268">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A269" s="1">
-        <v>46215</v>
-      </c>
-      <c r="B269" t="s">
-        <v>21</v>
-      </c>
-      <c r="C269">
-        <v>2051.4899999999998</v>
-      </c>
-      <c r="D269">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A270" s="1">
-        <v>46215</v>
-      </c>
-      <c r="B270" t="s">
-        <v>20</v>
-      </c>
-      <c r="C270">
-        <v>2140.66</v>
-      </c>
-      <c r="D270">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A271" s="1">
-        <v>46214</v>
-      </c>
-      <c r="B271" t="s">
-        <v>18</v>
-      </c>
-      <c r="C271">
-        <v>857.82</v>
-      </c>
-      <c r="D271">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A272" s="1">
-        <v>46214</v>
-      </c>
-      <c r="B272" t="s">
-        <v>17</v>
-      </c>
-      <c r="C272">
-        <v>1634.03</v>
-      </c>
-      <c r="D272">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A273" s="1">
-        <v>46214</v>
-      </c>
-      <c r="B273" t="s">
-        <v>16</v>
-      </c>
-      <c r="C273">
-        <v>1856.6</v>
-      </c>
-      <c r="D273">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A274" s="1">
-        <v>46214</v>
-      </c>
-      <c r="B274" t="s">
-        <v>21</v>
-      </c>
-      <c r="C274">
-        <v>2130.1</v>
-      </c>
-      <c r="D274">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A275" s="1">
-        <v>46214</v>
-      </c>
-      <c r="B275" t="s">
-        <v>20</v>
-      </c>
-      <c r="C275">
-        <v>1720.53</v>
-      </c>
-      <c r="D275">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A276" s="1">
-        <v>46213</v>
-      </c>
-      <c r="B276" t="s">
-        <v>18</v>
-      </c>
-      <c r="C276">
-        <v>932.92</v>
-      </c>
-      <c r="D276">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A277" s="1">
-        <v>46213</v>
-      </c>
-      <c r="B277" t="s">
-        <v>17</v>
-      </c>
-      <c r="C277">
-        <v>1930.36</v>
-      </c>
-      <c r="D277">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A278" s="1">
-        <v>46213</v>
-      </c>
-      <c r="B278" t="s">
-        <v>16</v>
-      </c>
-      <c r="C278">
-        <v>1930.19</v>
-      </c>
-      <c r="D278">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A279" s="1">
-        <v>46213</v>
-      </c>
-      <c r="B279" t="s">
-        <v>21</v>
-      </c>
-      <c r="C279">
-        <v>1950.89</v>
-      </c>
-      <c r="D279">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A280" s="1">
-        <v>46213</v>
-      </c>
-      <c r="B280" t="s">
-        <v>20</v>
-      </c>
-      <c r="C280">
-        <v>1905.24</v>
-      </c>
-      <c r="D280">
-        <v>23</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Used_cars_data.xlsx
+++ b/Used_cars_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\Used_Car_Generation_Citywise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB4137C-ADB6-475A-965C-00201C11088D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A2F839-9955-4738-A4D4-5C100038A3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{5C907EC6-8375-449B-912A-5B85C1E38DC1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{5C907EC6-8375-449B-912A-5B85C1E38DC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Reference" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="32">
   <si>
     <t>Day</t>
   </si>
@@ -684,7 +684,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F03664B9-21D8-4CE9-9CC2-213E093E66E2}">
-  <dimension ref="A1:D315"/>
+  <dimension ref="A1:D337"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -5100,6 +5100,314 @@
         <v>18</v>
       </c>
     </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A316" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B316" t="s">
+        <v>11</v>
+      </c>
+      <c r="C316">
+        <v>2275.46</v>
+      </c>
+      <c r="D316">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A317" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B317" t="s">
+        <v>7</v>
+      </c>
+      <c r="C317">
+        <v>892.94</v>
+      </c>
+      <c r="D317">
+        <v>12.34</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A318" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B318" t="s">
+        <v>8</v>
+      </c>
+      <c r="C318">
+        <v>1609.95</v>
+      </c>
+      <c r="D318">
+        <v>65.25</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A319" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B319" t="s">
+        <v>9</v>
+      </c>
+      <c r="C319">
+        <v>1236.8499999999999</v>
+      </c>
+      <c r="D319">
+        <v>27.93</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A320" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B320" t="s">
+        <v>29</v>
+      </c>
+      <c r="C320">
+        <v>654.12</v>
+      </c>
+      <c r="D320">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A321" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B321" t="s">
+        <v>18</v>
+      </c>
+      <c r="C321">
+        <v>1082.83</v>
+      </c>
+      <c r="D321">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A322" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B322" t="s">
+        <v>17</v>
+      </c>
+      <c r="C322">
+        <v>2160.94</v>
+      </c>
+      <c r="D322">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A323" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B323" t="s">
+        <v>16</v>
+      </c>
+      <c r="C323">
+        <v>2077.88</v>
+      </c>
+      <c r="D323">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A324" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B324" t="s">
+        <v>21</v>
+      </c>
+      <c r="C324">
+        <v>2051.4899999999998</v>
+      </c>
+      <c r="D324">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A325" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B325" t="s">
+        <v>20</v>
+      </c>
+      <c r="C325">
+        <v>2140.66</v>
+      </c>
+      <c r="D325">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A326" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B326" t="s">
+        <v>29</v>
+      </c>
+      <c r="C326">
+        <v>911.2</v>
+      </c>
+      <c r="D326">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A327" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B327" t="s">
+        <v>18</v>
+      </c>
+      <c r="C327">
+        <v>857.82</v>
+      </c>
+      <c r="D327">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A328" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B328" t="s">
+        <v>17</v>
+      </c>
+      <c r="C328">
+        <v>1634.03</v>
+      </c>
+      <c r="D328">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A329" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B329" t="s">
+        <v>16</v>
+      </c>
+      <c r="C329">
+        <v>1856.6</v>
+      </c>
+      <c r="D329">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A330" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B330" t="s">
+        <v>21</v>
+      </c>
+      <c r="C330">
+        <v>2130.1</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A331" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B331" t="s">
+        <v>20</v>
+      </c>
+      <c r="C331">
+        <v>1720.53</v>
+      </c>
+      <c r="D331">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A332" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B332" t="s">
+        <v>29</v>
+      </c>
+      <c r="C332">
+        <v>450.31</v>
+      </c>
+      <c r="D332">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A333" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B333" t="s">
+        <v>18</v>
+      </c>
+      <c r="C333">
+        <v>932.92</v>
+      </c>
+      <c r="D333">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A334" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B334" t="s">
+        <v>17</v>
+      </c>
+      <c r="C334">
+        <v>1930.36</v>
+      </c>
+      <c r="D334">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A335" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B335" t="s">
+        <v>16</v>
+      </c>
+      <c r="C335">
+        <v>1930.19</v>
+      </c>
+      <c r="D335">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A336" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B336" t="s">
+        <v>21</v>
+      </c>
+      <c r="C336">
+        <v>1950.89</v>
+      </c>
+      <c r="D336">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A337" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B337" t="s">
+        <v>20</v>
+      </c>
+      <c r="C337">
+        <v>1905.24</v>
+      </c>
+      <c r="D337">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5107,7 +5415,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19733ED7-6DA4-4FF9-B8AE-1C6E36A489FB}">
-  <dimension ref="A1:D261"/>
+  <dimension ref="A1:D283"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -8758,6 +9066,311 @@
         <v>50</v>
       </c>
     </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A262" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B262" t="s">
+        <v>18</v>
+      </c>
+      <c r="C262">
+        <v>1084.76</v>
+      </c>
+      <c r="D262">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A263" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B263" t="s">
+        <v>17</v>
+      </c>
+      <c r="C263">
+        <v>2162.6</v>
+      </c>
+      <c r="D263">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A264" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B264" t="s">
+        <v>16</v>
+      </c>
+      <c r="C264">
+        <v>2080.38</v>
+      </c>
+      <c r="D264">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A265" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B265" t="s">
+        <v>21</v>
+      </c>
+      <c r="C265">
+        <v>2058.1799999999998</v>
+      </c>
+      <c r="D265">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A266" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B266" t="s">
+        <v>20</v>
+      </c>
+      <c r="C266">
+        <v>2144.1799999999998</v>
+      </c>
+      <c r="D266">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A267" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B267" t="s">
+        <v>18</v>
+      </c>
+      <c r="C267">
+        <v>857.82</v>
+      </c>
+      <c r="D267">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A268" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B268" t="s">
+        <v>17</v>
+      </c>
+      <c r="C268">
+        <v>1634.03</v>
+      </c>
+      <c r="D268">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A269" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B269" t="s">
+        <v>16</v>
+      </c>
+      <c r="C269">
+        <v>1856.6</v>
+      </c>
+      <c r="D269">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A270" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B270" t="s">
+        <v>21</v>
+      </c>
+      <c r="C270">
+        <v>2130.1</v>
+      </c>
+      <c r="D270">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A271" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B271" t="s">
+        <v>20</v>
+      </c>
+      <c r="C271">
+        <v>1720.53</v>
+      </c>
+      <c r="D271">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A272" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B272" t="s">
+        <v>28</v>
+      </c>
+      <c r="C272">
+        <v>307.64999999999998</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A273" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B273" t="s">
+        <v>18</v>
+      </c>
+      <c r="C273">
+        <v>932.92</v>
+      </c>
+      <c r="D273">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A274" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B274" t="s">
+        <v>17</v>
+      </c>
+      <c r="C274">
+        <v>1930.36</v>
+      </c>
+      <c r="D274">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A275" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B275" t="s">
+        <v>16</v>
+      </c>
+      <c r="C275">
+        <v>1930.19</v>
+      </c>
+      <c r="D275">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A276" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B276" t="s">
+        <v>21</v>
+      </c>
+      <c r="C276">
+        <v>1950.89</v>
+      </c>
+      <c r="D276">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A277" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B277" t="s">
+        <v>20</v>
+      </c>
+      <c r="C277">
+        <v>1905.24</v>
+      </c>
+      <c r="D277">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A278" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B278" t="s">
+        <v>28</v>
+      </c>
+      <c r="C278">
+        <v>988.33</v>
+      </c>
+      <c r="D278">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A279" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B279" t="s">
+        <v>18</v>
+      </c>
+      <c r="C279">
+        <v>1005.63</v>
+      </c>
+      <c r="D279">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A280" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B280" t="s">
+        <v>17</v>
+      </c>
+      <c r="C280">
+        <v>2474.44</v>
+      </c>
+      <c r="D280">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A281" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B281" t="s">
+        <v>16</v>
+      </c>
+      <c r="C281">
+        <v>2103.42</v>
+      </c>
+      <c r="D281">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A282" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B282" t="s">
+        <v>21</v>
+      </c>
+      <c r="C282">
+        <v>2028.31</v>
+      </c>
+      <c r="D282">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A283" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B283" t="s">
+        <v>20</v>
+      </c>
+      <c r="C283">
+        <v>2097.2199999999998</v>
+      </c>
+      <c r="D283">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Used_cars_data.xlsx
+++ b/Used_cars_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\Used_Car_Generation_Citywise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A2F839-9955-4738-A4D4-5C100038A3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC42971-1029-499B-9488-B0ABBC1EFA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{5C907EC6-8375-449B-912A-5B85C1E38DC1}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="33">
   <si>
     <t>Day</t>
   </si>
@@ -137,6 +137,9 @@
   </si>
   <si>
     <t>Meta-Whatsapp</t>
+  </si>
+  <si>
+    <t>Nashik-Whatsup-Leads -13thJuly</t>
   </si>
 </sst>
 </file>
@@ -684,7 +687,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F03664B9-21D8-4CE9-9CC2-213E093E66E2}">
-  <dimension ref="A1:D337"/>
+  <dimension ref="A1:D341"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -5408,6 +5411,62 @@
         <v>23</v>
       </c>
     </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A338" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B338" t="s">
+        <v>11</v>
+      </c>
+      <c r="C338">
+        <v>1225.19</v>
+      </c>
+      <c r="D338">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A339" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B339" t="s">
+        <v>7</v>
+      </c>
+      <c r="C339">
+        <v>1049.3599999999999</v>
+      </c>
+      <c r="D339">
+        <v>14.96</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A340" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B340" t="s">
+        <v>8</v>
+      </c>
+      <c r="C340">
+        <v>1419.88</v>
+      </c>
+      <c r="D340">
+        <v>43.91</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A341" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B341" t="s">
+        <v>9</v>
+      </c>
+      <c r="C341">
+        <v>1138.71</v>
+      </c>
+      <c r="D341">
+        <v>24.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5415,8 +5474,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19733ED7-6DA4-4FF9-B8AE-1C6E36A489FB}">
-  <dimension ref="A1:D283"/>
+  <dimension ref="A1:D290"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -9371,6 +9433,104 @@
         <v>29</v>
       </c>
     </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A284" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B284" t="s">
+        <v>20</v>
+      </c>
+      <c r="C284">
+        <v>1818.73</v>
+      </c>
+      <c r="D284">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A285" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B285" t="s">
+        <v>21</v>
+      </c>
+      <c r="C285">
+        <v>2005.13</v>
+      </c>
+      <c r="D285">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A286" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B286" t="s">
+        <v>16</v>
+      </c>
+      <c r="C286">
+        <v>2093.6799999999998</v>
+      </c>
+      <c r="D286">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A287" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B287" t="s">
+        <v>17</v>
+      </c>
+      <c r="C287">
+        <v>2048.29</v>
+      </c>
+      <c r="D287">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A288" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B288" t="s">
+        <v>18</v>
+      </c>
+      <c r="C288">
+        <v>1104.32</v>
+      </c>
+      <c r="D288">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A289" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B289" t="s">
+        <v>29</v>
+      </c>
+      <c r="C289">
+        <v>506.1</v>
+      </c>
+      <c r="D289">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A290" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B290" t="s">
+        <v>32</v>
+      </c>
+      <c r="C290">
+        <v>708.99</v>
+      </c>
+      <c r="D290">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Used_cars_data.xlsx
+++ b/Used_cars_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\Used_Car_Generation_Citywise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC42971-1029-499B-9488-B0ABBC1EFA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B4A967-DB72-411F-9B03-91ECF869511B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{5C907EC6-8375-449B-912A-5B85C1E38DC1}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="34">
   <si>
     <t>Day</t>
   </si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>Nashik-Whatsup-Leads -13thJuly</t>
+  </si>
+  <si>
+    <t>UCR-Lead-Luxury-Cart-Classified-Jan25</t>
   </si>
 </sst>
 </file>
@@ -687,7 +690,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F03664B9-21D8-4CE9-9CC2-213E093E66E2}">
-  <dimension ref="A1:D341"/>
+  <dimension ref="A1:D345"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -5467,6 +5470,62 @@
         <v>24.12</v>
       </c>
     </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A342" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B342" t="s">
+        <v>11</v>
+      </c>
+      <c r="C342">
+        <v>1074</v>
+      </c>
+      <c r="D342">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A343" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B343" t="s">
+        <v>7</v>
+      </c>
+      <c r="C343">
+        <v>1684.67</v>
+      </c>
+      <c r="D343">
+        <v>19.649999999999999</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A344" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B344" t="s">
+        <v>8</v>
+      </c>
+      <c r="C344">
+        <v>1481.8</v>
+      </c>
+      <c r="D344">
+        <v>37.65</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A345" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B345" t="s">
+        <v>9</v>
+      </c>
+      <c r="C345">
+        <v>1133.3499999999999</v>
+      </c>
+      <c r="D345">
+        <v>21.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5474,7 +5533,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19733ED7-6DA4-4FF9-B8AE-1C6E36A489FB}">
-  <dimension ref="A1:D290"/>
+  <dimension ref="A1:D300"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -9531,6 +9590,143 @@
         <v>21</v>
       </c>
     </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A291" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B291" t="s">
+        <v>21</v>
+      </c>
+      <c r="C291">
+        <v>499.23</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A292" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B292" t="s">
+        <v>20</v>
+      </c>
+      <c r="C292">
+        <v>844.1</v>
+      </c>
+      <c r="D292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A293" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B293" t="s">
+        <v>19</v>
+      </c>
+      <c r="C293">
+        <v>371.04</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A294" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B294" t="s">
+        <v>32</v>
+      </c>
+      <c r="C294">
+        <v>1862.4</v>
+      </c>
+      <c r="D294">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A295" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B295" t="s">
+        <v>18</v>
+      </c>
+      <c r="C295">
+        <v>941.11</v>
+      </c>
+      <c r="D295">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A296" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B296" t="s">
+        <v>17</v>
+      </c>
+      <c r="C296">
+        <v>1804.81</v>
+      </c>
+      <c r="D296">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A297" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B297" t="s">
+        <v>16</v>
+      </c>
+      <c r="C297">
+        <v>2012.4</v>
+      </c>
+      <c r="D297">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A298" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B298" t="s">
+        <v>21</v>
+      </c>
+      <c r="C298">
+        <v>663.85</v>
+      </c>
+      <c r="D298">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A299" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B299" t="s">
+        <v>20</v>
+      </c>
+      <c r="C299">
+        <v>716.27</v>
+      </c>
+      <c r="D299">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A300" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B300" t="s">
+        <v>33</v>
+      </c>
+      <c r="C300">
+        <v>468.11</v>
+      </c>
+      <c r="D300">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
